--- a/output/Data and Chart Outputs/sri_lanka_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/sri_lanka_power_generation_daily.xlsx
@@ -24,8 +24,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,12 +65,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,7 +160,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Sri Lanka power generation by source (PUCSL / CEB) (to Oct/26)</a:t>
+              <a:t>Sri Lanka power generation by source (PUCSL / CEB) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -189,12 +190,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$47</f>
+              <f>'Chart'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$47</f>
+              <f>'Chart'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$47</f>
+              <f>'Chart'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$47</f>
+              <f>'Chart'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$47</f>
+              <f>'Chart'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$47</f>
+              <f>'Chart'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +274,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$47</f>
+              <f>'Chart'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$47</f>
+              <f>'Chart'!$E$2:$E$46</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +302,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$47</f>
+              <f>'Chart'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$47</f>
+              <f>'Chart'!$F$2:$F$46</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +330,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$47</f>
+              <f>'Chart'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$47</f>
+              <f>'Chart'!$G$2:$G$46</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +358,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$47</f>
+              <f>'Chart'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$47</f>
+              <f>'Chart'!$H$2:$H$46</f>
             </numRef>
           </val>
         </ser>
@@ -462,7 +463,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Sri Lanka total dispatch (PUCSL / CEB) (to Oct/26)</a:t>
+              <a:t>Sri Lanka total dispatch (PUCSL / CEB) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -498,12 +499,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Demand'!$A$2:$A$47</f>
+              <f>'Chart - Demand'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Demand'!$B$2:$B$47</f>
+              <f>'Chart - Demand'!$B$2:$B$46</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -534,12 +535,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Demand'!$A$2:$A$47</f>
+              <f>'Chart - Demand'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Demand'!$C$2:$C$47</f>
+              <f>'Chart - Demand'!$C$2:$C$46</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1010,7 +1011,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -1025,7 +1025,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1051,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1100,7 +1099,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B2" t="n">
@@ -1126,7 +1125,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B3" t="n">
@@ -1152,7 +1151,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B4" t="n">
@@ -1178,7 +1177,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B5" t="n">
@@ -1204,7 +1203,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B6" t="n">
@@ -1230,7 +1229,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B7" t="n">
@@ -1256,7 +1255,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B8" t="n">
@@ -1282,7 +1281,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B9" t="n">
@@ -1308,7 +1307,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B10" t="n">
@@ -1334,7 +1333,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B11" t="n">
@@ -1360,7 +1359,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B12" t="n">
@@ -1386,7 +1385,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B13" t="n">
@@ -1412,7 +1411,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B14" t="n">
@@ -1438,7 +1437,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B15" t="n">
@@ -1464,7 +1463,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B16" t="n">
@@ -1490,7 +1489,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B17" t="n">
@@ -1516,7 +1515,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B18" t="n">
@@ -1542,7 +1541,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B19" t="n">
@@ -1568,7 +1567,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B20" t="n">
@@ -1594,7 +1593,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B21" t="n">
@@ -1620,7 +1619,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B22" t="n">
@@ -1646,7 +1645,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B23" t="n">
@@ -1672,7 +1671,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B24" t="n">
@@ -1698,7 +1697,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B25" t="n">
@@ -1724,7 +1723,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B26" t="n">
@@ -1750,7 +1749,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B27" t="n">
@@ -1776,7 +1775,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B28" t="n">
@@ -1802,7 +1801,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B29" t="n">
@@ -1828,7 +1827,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B30" t="n">
@@ -1854,7 +1853,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B31" t="n">
@@ -1880,7 +1879,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B32" t="n">
@@ -1906,7 +1905,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B33" t="n">
@@ -1932,7 +1931,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B34" t="n">
@@ -1958,7 +1957,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B35" t="n">
@@ -1984,7 +1983,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B36" t="n">
@@ -2010,7 +2009,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B37" t="n">
@@ -2036,7 +2035,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B38" t="n">
@@ -2062,7 +2061,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B39" t="n">
@@ -2088,7 +2087,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B40" t="n">
@@ -2114,7 +2113,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B41" t="n">
@@ -2140,7 +2139,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B42" t="n">
@@ -2166,7 +2165,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B43" t="n">
@@ -2192,7 +2191,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B44" t="n">
@@ -2218,7 +2217,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B45" t="n">
@@ -2244,7 +2243,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B46" t="n">
@@ -2267,32 +2266,6 @@
       </c>
       <c r="H46" t="n">
         <v>292.7016</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2307,7 +2280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2331,7 +2304,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B2" t="n">
@@ -2342,7 +2315,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B3" t="n">
@@ -2353,7 +2326,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B4" t="n">
@@ -2364,7 +2337,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B5" t="n">
@@ -2375,7 +2348,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B6" t="n">
@@ -2386,7 +2359,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B7" t="n">
@@ -2397,7 +2370,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B8" t="n">
@@ -2408,7 +2381,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B9" t="n">
@@ -2419,7 +2392,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B10" t="n">
@@ -2430,7 +2403,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B11" t="n">
@@ -2441,7 +2414,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B12" t="n">
@@ -2452,7 +2425,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B13" t="n">
@@ -2463,7 +2436,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B14" t="n">
@@ -2474,7 +2447,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B15" t="n">
@@ -2485,7 +2458,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B16" t="n">
@@ -2496,7 +2469,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B17" t="n">
@@ -2507,7 +2480,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B18" t="n">
@@ -2518,7 +2491,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B19" t="n">
@@ -2529,7 +2502,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B20" t="n">
@@ -2540,7 +2513,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B21" t="n">
@@ -2551,7 +2524,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B22" t="n">
@@ -2562,7 +2535,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B23" t="n">
@@ -2573,7 +2546,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B24" t="n">
@@ -2584,7 +2557,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B25" t="n">
@@ -2595,7 +2568,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B26" t="n">
@@ -2606,7 +2579,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B27" t="n">
@@ -2617,7 +2590,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B28" t="n">
@@ -2628,7 +2601,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B29" t="n">
@@ -2639,7 +2612,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B30" t="n">
@@ -2650,7 +2623,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B31" t="n">
@@ -2661,7 +2634,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B32" t="n">
@@ -2672,7 +2645,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B33" t="n">
@@ -2683,7 +2656,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B34" t="n">
@@ -2694,7 +2667,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B35" t="n">
@@ -2705,7 +2678,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B36" t="n">
@@ -2716,7 +2689,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B37" t="n">
@@ -2727,7 +2700,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B38" t="n">
@@ -2738,7 +2711,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B39" t="n">
@@ -2749,7 +2722,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B40" t="n">
@@ -2760,7 +2733,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B41" t="n">
@@ -2771,7 +2744,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B42" t="n">
@@ -2782,7 +2755,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B43" t="n">
@@ -2793,7 +2766,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B44" t="n">
@@ -2804,7 +2777,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B45" t="n">
@@ -2815,7 +2788,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B46" t="n">
@@ -2823,17 +2796,6 @@
       </c>
       <c r="C46" t="n">
         <v>2871.933333333333</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2848,7 +2810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1372"/>
+  <dimension ref="A1:K1370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50820,76 +50782,6 @@
         <v>64265.9</v>
       </c>
       <c r="K1370" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="1371">
-      <c r="A1371" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="C1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1371" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="1372">
-      <c r="A1372" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="C1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1372" t="n">
         <v>96</v>
       </c>
     </row>
@@ -50904,7 +50796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1372"/>
+  <dimension ref="A1:D1370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70092,34 +69984,6 @@
         <v>3044</v>
       </c>
       <c r="D1370" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1371">
-      <c r="A1371" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="C1371" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1371" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1372">
-      <c r="A1372" s="4" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="C1372" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1372" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70134,7 +69998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU122"/>
+  <dimension ref="A1:AU120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84596,16 +84460,6 @@
       </c>
       <c r="AU120" t="n">
         <v>-5.76</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="n">
-        <v>46296</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="4" t="n">
-        <v>46297</v>
       </c>
     </row>
   </sheetData>
